--- a/tests/fixtures/birch-plaza/client.xlsx
+++ b/tests/fixtures/birch-plaza/client.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>Birch Plaza — Rent Roll</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Rent Steps</t>
   </si>
   <si>
+    <t>% Rent</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>12/31/2031</t>
   </si>
   <si>
+    <t>Breakpoint $600,000; Overage 6%</t>
+  </si>
+  <si>
     <t>500</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
   </si>
   <si>
     <t>12/31/2032</t>
+  </si>
+  <si>
+    <t>Breakpoint $500,000; Overage 7%</t>
   </si>
   <si>
     <t>600</t>
@@ -498,10 +507,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -526,8 +535,11 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -552,8 +564,11 @@
       <c r="H2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -578,160 +593,181 @@
       <c r="H4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>20000</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>2500</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>3000</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>3500</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>1200</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>10000</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10">
         <v>105000</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
         <v>1</v>
       </c>
     </row>
